--- a/plan_limpieza.xlsx
+++ b/plan_limpieza.xlsx
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">Versión</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-11-05</t>
+    <t xml:space="preserve">2025-11-06</t>
   </si>
   <si>
     <t xml:space="preserve">Autor</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-11-05 23:05:01</t>
+    <t xml:space="preserve">2025-11-06 18:54:21</t>
   </si>
   <si>
     <t xml:space="preserve">Descripción</t>
@@ -12476,8 +12476,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;BPlan de Limpieza – ACNUR&amp;B&amp;C&amp;RVersión: 2025-11-05</oddHeader>
-    <oddFooter>&amp;L2025-11-05 23:05&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;BPlan de Limpieza – ACNUR&amp;B&amp;C&amp;RVersión: 2025-11-06</oddHeader>
+    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -12530,8 +12530,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-05</oddHeader>
-    <oddFooter>&amp;L2025-11-05 23:05&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
+    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -12675,8 +12675,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-05</oddHeader>
-    <oddFooter>&amp;L2025-11-05 23:05&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
+    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -15374,8 +15374,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-05</oddHeader>
-    <oddFooter>&amp;L2025-11-05 23:05&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
+    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -16762,8 +16762,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-05</oddHeader>
-    <oddFooter>&amp;L2025-11-05 23:05&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
+    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -16869,8 +16869,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-05</oddHeader>
-    <oddFooter>&amp;L2025-11-05 23:05&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
+    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -17563,8 +17563,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;BPlan de Limpieza – ACNUR&amp;B&amp;C&amp;RVersión: 2025-11-05</oddHeader>
-    <oddFooter>&amp;L2025-11-05 23:05&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;BPlan de Limpieza – ACNUR&amp;B&amp;C&amp;RVersión: 2025-11-06</oddHeader>
+    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/plan_limpieza.xlsx
+++ b/plan_limpieza.xlsx
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">Versión</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-11-06</t>
+    <t xml:space="preserve">2025-11-14</t>
   </si>
   <si>
     <t xml:space="preserve">Autor</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-11-06 18:54:21</t>
+    <t xml:space="preserve">2025-11-14 18:29:07</t>
   </si>
   <si>
     <t xml:space="preserve">Descripción</t>
@@ -12476,8 +12476,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;BPlan de Limpieza – ACNUR&amp;B&amp;C&amp;RVersión: 2025-11-06</oddHeader>
-    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;BPlan de Limpieza – ACNUR&amp;B&amp;C&amp;RVersión: 2025-11-14</oddHeader>
+    <oddFooter>&amp;L2025-11-14 18:29&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -12530,8 +12530,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
-    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-14</oddHeader>
+    <oddFooter>&amp;L2025-11-14 18:29&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -12675,8 +12675,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
-    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-14</oddHeader>
+    <oddFooter>&amp;L2025-11-14 18:29&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -15374,8 +15374,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
-    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-14</oddHeader>
+    <oddFooter>&amp;L2025-11-14 18:29&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -16762,8 +16762,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
-    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-14</oddHeader>
+    <oddFooter>&amp;L2025-11-14 18:29&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -16869,8 +16869,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-06</oddHeader>
-    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;C&amp;RVersión: 2025-11-14</oddHeader>
+    <oddFooter>&amp;L2025-11-14 18:29&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -17563,8 +17563,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="0" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;BPlan de Limpieza – ACNUR&amp;B&amp;C&amp;RVersión: 2025-11-06</oddHeader>
-    <oddFooter>&amp;L2025-11-06 18:54&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
+    <oddHeader>&amp;L&amp;BPlan de Limpieza – ACNUR&amp;B&amp;C&amp;RVersión: 2025-11-14</oddHeader>
+    <oddFooter>&amp;L2025-11-14 18:29&amp;C&amp;P de &amp;N&amp;RACNUR</oddFooter>
   </headerFooter>
 </worksheet>
 </file>